--- a/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
@@ -8,48 +8,47 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68655C08-065D-4BC8-ABD4-8883C94D31DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84173879-A876-4F8F-8D71-F80C6BBA6E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="28" activeTab="31" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Paclitaxel" sheetId="1" r:id="rId1"/>
     <sheet name="Alpesilib" sheetId="2" r:id="rId2"/>
-    <sheet name="Anastrazole" sheetId="3" r:id="rId3"/>
+    <sheet name="Anastrozole" sheetId="3" r:id="rId3"/>
     <sheet name="Fulvestrant" sheetId="4" r:id="rId4"/>
     <sheet name="Palbociclib" sheetId="5" r:id="rId5"/>
     <sheet name="Abemaciclib" sheetId="6" r:id="rId6"/>
     <sheet name="Atezolizumab" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId8"/>
-    <sheet name="Bevacizumab" sheetId="8" r:id="rId9"/>
-    <sheet name="Capivasertib" sheetId="9" r:id="rId10"/>
-    <sheet name="Dostarlimab" sheetId="10" r:id="rId11"/>
-    <sheet name="Elacestrant" sheetId="11" r:id="rId12"/>
-    <sheet name="Entrectinib" sheetId="12" r:id="rId13"/>
-    <sheet name="Everolimus" sheetId="13" r:id="rId14"/>
-    <sheet name="Exemestane" sheetId="14" r:id="rId15"/>
-    <sheet name="Lapatinib" sheetId="15" r:id="rId16"/>
-    <sheet name="Larotrectinib" sheetId="16" r:id="rId17"/>
-    <sheet name="Letrozole" sheetId="17" r:id="rId18"/>
-    <sheet name="Margetuximab" sheetId="18" r:id="rId19"/>
-    <sheet name="Neratinib" sheetId="19" r:id="rId20"/>
-    <sheet name="Olaparib" sheetId="20" r:id="rId21"/>
-    <sheet name="Pembrolizumab" sheetId="21" r:id="rId22"/>
-    <sheet name="Pertuzumab" sheetId="22" r:id="rId23"/>
-    <sheet name="Ribociclib" sheetId="23" r:id="rId24"/>
-    <sheet name="Sacituzumab govitecan" sheetId="24" r:id="rId25"/>
-    <sheet name="Selpercatinib" sheetId="25" r:id="rId26"/>
-    <sheet name="Talazoparib" sheetId="26" r:id="rId27"/>
-    <sheet name="Tamoxifen" sheetId="27" r:id="rId28"/>
-    <sheet name="Toremifene" sheetId="28" r:id="rId29"/>
-    <sheet name="Trastuzumab" sheetId="29" r:id="rId30"/>
-    <sheet name="Trastuzumab deruxtecan" sheetId="30" r:id="rId31"/>
-    <sheet name="Trastuzumab emtansine" sheetId="31" r:id="rId32"/>
-    <sheet name="Tucatinib" sheetId="32" r:id="rId33"/>
+    <sheet name="Bevacizumab" sheetId="8" r:id="rId8"/>
+    <sheet name="Capivasertib" sheetId="9" r:id="rId9"/>
+    <sheet name="Dostarlimab" sheetId="10" r:id="rId10"/>
+    <sheet name="Elacestrant" sheetId="11" r:id="rId11"/>
+    <sheet name="Entrectinib" sheetId="12" r:id="rId12"/>
+    <sheet name="Everolimus" sheetId="13" r:id="rId13"/>
+    <sheet name="Exemestane" sheetId="14" r:id="rId14"/>
+    <sheet name="Lapatinib" sheetId="15" r:id="rId15"/>
+    <sheet name="Larotrectinib" sheetId="16" r:id="rId16"/>
+    <sheet name="Letrozole" sheetId="17" r:id="rId17"/>
+    <sheet name="Margetuximab" sheetId="18" r:id="rId18"/>
+    <sheet name="Neratinib" sheetId="19" r:id="rId19"/>
+    <sheet name="Olaparib" sheetId="20" r:id="rId20"/>
+    <sheet name="Pembrolizumab" sheetId="21" r:id="rId21"/>
+    <sheet name="Pertuzumab" sheetId="22" r:id="rId22"/>
+    <sheet name="Ribociclib" sheetId="23" r:id="rId23"/>
+    <sheet name="Sacituzumab govitecan" sheetId="24" r:id="rId24"/>
+    <sheet name="Selpercatinib" sheetId="25" r:id="rId25"/>
+    <sheet name="Talazoparib" sheetId="26" r:id="rId26"/>
+    <sheet name="Tamoxifen" sheetId="27" r:id="rId27"/>
+    <sheet name="Toremifene" sheetId="28" r:id="rId28"/>
+    <sheet name="Trastuzumab" sheetId="29" r:id="rId29"/>
+    <sheet name="Trastuzumab deruxtecan" sheetId="30" r:id="rId30"/>
+    <sheet name="Trastuzumab emtansine" sheetId="31" r:id="rId31"/>
+    <sheet name="Tucatinib" sheetId="32" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Alpesilib!$C$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Anastrazole!$C$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Anastrozole!$C$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Fulvestrant!$C$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paclitaxel!$C$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Palbociclib!$C$1:$C$10</definedName>
@@ -75,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1061">
   <si>
     <t>Pathway (Human)</t>
   </si>
@@ -732,9 +731,6 @@
     <t>An increase in Treg and MDSC-associated pathways (e.g. high CCL2, IL-6, ARG1) leads to accumulation of suppressive cells that inhibit effector T-cells. Atezolizumab efficacy is reduced in tumors with high FoxP3⁺ Tregs or CD11b⁺ myeloid infiltration. For instance, elevation of IL-6 and IL-8 in plasma was associated with poorer outcomes (seen in other solid tumors). Reducing these pathways (via downregulation or targeted agents) is thought to improve response.</t>
   </si>
   <si>
-    <t>Effect of Bevacizumab</t>
-  </si>
-  <si>
     <t>Source(s)</t>
   </si>
   <si>
@@ -7340,37 +7336,678 @@
     <t>High NK-cell signaling suggests immune surveillance. Again, not directly targeted by tucatinib, but may indicate a tumor more amenable to immunogenic cell death.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Pathway                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Administration </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Regulation </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Effect    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rationale                                                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ref(s)                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Before  </t>
-  </si>
-  <si>
-    <t>Resistance</t>
-  </si>
-  <si>
-    <t>Sensistive</t>
-  </si>
-  <si>
-    <t>After</t>
+    <t>Rationale (Mechanism)</t>
+  </si>
+  <si>
+    <r>
+      <t>Reactome R-HSA-1227990 (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ERBB2 signaling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>T-DM1 binding inhibits HER2-driven RAS/MAPK and PI3K/AKT signaling, halting proliferation. Loss of this inhibition confers resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t>KEGG:hsa04012 (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ErbB signaling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Similar to above: HER2 blockade suppresses downstream pro-survival signals.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PI3K/AKT/mTOR signaling</t>
+    </r>
+  </si>
+  <si>
+    <t>Indirectly inhibited by HER2 targeting. Constitutive PI3K/AKT activation blunts T-DM1 effect, causing resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KRAS signaling up</t>
+    </r>
+  </si>
+  <si>
+    <t>HER2 blockade reduces RAS/MAPK signaling. KRAS/RAS hyperactivation drives resistance by bypassing HER2.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>G2M Checkpoint</t>
+    </r>
+  </si>
+  <si>
+    <t>Upregulation (high CCNB1/CDC20) means active cycling into mitosis; cells arrested by DM1-mediated mitotic blockade.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E2F Targets</t>
+    </r>
+  </si>
+  <si>
+    <t>E2F activation reflects cell-cycle progression; T-DM1 requires dividing cells. CCNB1 suppression reduces efficacy.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apoptosis</t>
+    </r>
+  </si>
+  <si>
+    <t>Activation of apoptotic programs (caspases, etc.) enables cell death after DM1 damage.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Interferon Gamma Response</t>
+    </r>
+  </si>
+  <si>
+    <t>Reflects IFNγ-driven immune activation. Enhanced TIL/IFNγ signaling correlates with better ADC response and can prime ADCC.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reactome </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Endocytosis</t>
+    </r>
+  </si>
+  <si>
+    <t>Increased receptor-mediated uptake of HER2–T-DM1 complex leads to more DM1 release. Loss of endocytosis components causes resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reactome </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lysosome</t>
+    </r>
+  </si>
+  <si>
+    <t>Efficient lysosomal degradation of T-DM1 releases DM1 payload. Impaired lysosomal function (e.g. SLC46A3 loss) causes resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reactome </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ABC transporters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (KEGG 02010)</t>
+    </r>
+  </si>
+  <si>
+    <t>Overexpression of MDR1/P-gp (ABCB1) and related pumps effluxes DM1, reducing intracellular drug. Upregulation confers resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t>Reactome R-HSA-5663201 (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RAS activation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hyperactivation of RAS/MAPK (e.g. via RTK bypass) overcomes HER2 blockade, promoting survival and resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DNA Repair</t>
+    </r>
+  </si>
+  <si>
+    <t>(Speculative) Enhanced DNA repair might counter DNA damage from any secondary effects of DM1; not well-established for T-DM1 specifically.</t>
+  </si>
+  <si>
+    <t>– (no direct evidence)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TNFα/NF-κB signaling</t>
+    </r>
+  </si>
+  <si>
+    <t>Activation of NF-κB can promote survival and drug resistance in many settings; may blunt ADC-induced apoptosis.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GO: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Caveola-mediated endocytosis</t>
+    </r>
+  </si>
+  <si>
+    <t>Increased caveolin-1 (CAV1) enhances T-DM1 uptake in some models. Downregulation lowers sensitivity.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GO: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Microtubule cytoskeleton organization</t>
+    </r>
+  </si>
+  <si>
+    <t>Reduced microtubule assembly factors (TUBB etc.) may impair DM1 binding, although evidence is limited.</t>
+  </si>
+  <si>
+    <r>
+      <t>Reactome R-HSA-69409 (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ubiquitin-mediated proteolysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Upregulation of ubiquitination pathways (e.g. altered lysosomal targeting) could degrade HER2–T-DM1 complexes before DM1 release, impairing efficacy.</t>
+  </si>
+  <si>
+    <t>– (emerging)</t>
+  </si>
+  <si>
+    <t>(As above) Constitutive activation bypasses HER2 blockade.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hallmark </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Estrogen Response</t>
+    </r>
+  </si>
+  <si>
+    <t>Not directly modulated by T-DM1; influences sensitivity only via effect on HER2+ luminal tumors, not a direct T-DM1 pathway.</t>
+  </si>
+  <si>
+    <t>Pathway (database IDs)</t>
+  </si>
+  <si>
+    <t>Regulation by Trastuzumab</t>
+  </si>
+  <si>
+    <t>Sensitivity/Resistance Association</t>
+  </si>
+  <si>
+    <t>Evidence</t>
+  </si>
+  <si>
+    <r>
+      <t>ErbB/HER2 signaling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Reactome R-HSA-1227986; KEGG hsa04012)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sensitivity ↑ when HER2 is targetable; Resistance if HER2 signaling persists (e.g. p95-HER2)</t>
+  </si>
+  <si>
+    <t>Trastuzumab binds HER2, inducing receptor downmodulation and blocking downstream signals. High HER2 expression is required for effect.</t>
+  </si>
+  <si>
+    <r>
+      <t>PI3K/AKT/mTOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (R-HSA-2219528; KEGG hsa04151)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistance when ↑ (PIK3CA mutation, PTEN loss); Sensitivity when ↓</t>
+  </si>
+  <si>
+    <t>Normally activated downstream of HER2; its inhibition leads to decreased growth. Constitutive PI3K/AKT activation drives trastuzumab resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t>MAPK/ERK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (R-HSA-5683057; KEGG hsa04010)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistance when ↑ (e.g. RAS mutation); Sensitivity when ↓</t>
+  </si>
+  <si>
+    <t>HER2 blockade reduces Ras/Raf/ERK signaling. Cells require MAPK signaling for proliferation; trastuzumab downregulates this cascade.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cell Cycle (G1/S)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (R-HSA-1640170; KEGG hsa04110)</t>
+    </r>
+  </si>
+  <si>
+    <t>↑ (arrest)</t>
+  </si>
+  <si>
+    <t>Resistance when cell-cycle inhibitors lost; Sensitivity when arrest ↑</t>
+  </si>
+  <si>
+    <t>Trastuzumab induces G1 arrest via p27^Kip1 upregulation, halting proliferation. Loss of p27/↑CDK2 leads to resistance.</t>
+  </si>
+  <si>
+    <r>
+      <t>Apoptosis (intrinsic/extrinsic)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (R-HSA-109581; KEGG hsa04210)</t>
+    </r>
+  </si>
+  <si>
+    <t>↑ (promoted)</t>
+  </si>
+  <si>
+    <t>Resistance when anti-apoptotic signals ↑ (e.g. STAT3/BCL2); Sensitivity when apoptosis ↑</t>
+  </si>
+  <si>
+    <t>HER2 inhibition can activate apoptosis (e.g. via p53, death receptors). Trastuzumab can sensitize cells to apoptotic death. Resistance pathways (Notch/STAT3) upregulate anti-apoptotic signals.</t>
+  </si>
+  <si>
+    <t>(anti-apoptotic via Notch)</t>
+  </si>
+  <si>
+    <r>
+      <t>FcγR signaling / ADCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (KEGG hsa04666; GO:0038094)</t>
+    </r>
+  </si>
+  <si>
+    <t>Engaged (immune)</t>
+  </si>
+  <si>
+    <t>Sensitivity when active (strong ADCC); Resistance if impaired (FCGR polymorphisms)</t>
+  </si>
+  <si>
+    <t>Trastuzumab-bound cells trigger Fcγ receptors on NK cells, leading to cytotoxic killing. Effective immune engagement enhances tumor clearance.</t>
+  </si>
+  <si>
+    <r>
+      <t>NK cell cytotoxicity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (KEGG hsa04650)</t>
+    </r>
+  </si>
+  <si>
+    <t>Similar to ADCC above</t>
+  </si>
+  <si>
+    <t>Involves perforin/granzyme-mediated killing of trastuzumab-labeled cells. Robust NK response correlates with response.</t>
+  </si>
+  <si>
+    <t>(Related to ADCC; no direct ref)</t>
+  </si>
+  <si>
+    <r>
+      <t>Angiogenesis (VEGF)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Reactome e.g. R-HSA-381426; KEGG hsa04370)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistance when angiogenesis ↑; Sensitivity when ↓</t>
+  </si>
+  <si>
+    <t>Trastuzumab inhibits tumor angiogenesis, starving tumor. High VEGF-driven angiogenesis may counteract this effect.</t>
+  </si>
+  <si>
+    <r>
+      <t>Notch/STAT3 signaling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Reactome R-HSA-1640470; R-HSA-9031628)</t>
+    </r>
+  </si>
+  <si>
+    <t>↑ in resistance</t>
+  </si>
+  <si>
+    <t>Resistance when ↑; Sensitivity when ↓</t>
+  </si>
+  <si>
+    <t>Not directly targeted by trastuzumab. After HER2 blockade, Jagged1/Notch1 and STAT3 become upregulated, driving cell proliferation, stemness and survival. Inhibiting Notch/STAT3 can restore sensitivity.</t>
+  </si>
+  <si>
+    <r>
+      <t>JAK/STAT (IL-6) pathway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (KEGG hsa04630)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistance when IL-6/JAK-STAT ↑</t>
+  </si>
+  <si>
+    <t>Often activated downstream of Notch/STAT3 or inflammatory cytokines, promoting survival. (No direct citation)</t>
+  </si>
+  <si>
+    <t>(Implied by Notch/STAT3 data)</t>
+  </si>
+  <si>
+    <r>
+      <t>Cell adhesion/EMT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (GO/MSigDB terms)</t>
+    </r>
+  </si>
+  <si>
+    <t>Resistance when EMT ↑</t>
+  </si>
+  <si>
+    <t>Not a direct trastuzumab effect, but HER2 blockade can influence EMT markers. EMT may be linked to stem-like, trastuzumab-resistant phenotype.</t>
+  </si>
+  <si>
+    <t>(No direct citation)</t>
+  </si>
+  <si>
+    <t>Effect of Bevacizumab baseline</t>
   </si>
 </sst>
 </file>
@@ -8003,220 +8640,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74906B5F-BBD2-4E50-AA59-4D76843BE3DD}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A417E582-1074-4E3F-A381-7D1E4C5C9732}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8229,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
@@ -8240,22 +8663,22 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -8264,13 +8687,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -8279,13 +8702,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -8294,28 +8717,28 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -8324,13 +8747,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -8339,13 +8762,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -8354,13 +8777,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -8369,13 +8792,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -8384,13 +8807,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -8399,25 +8822,222 @@
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E13" s="2" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC56BB7C-FEA4-4B85-8130-F198D0578D61}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -8426,203 +9046,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC56BB7C-FEA4-4B85-8130-F198D0578D61}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5758C6-ECFE-417C-B9EA-14BCA8C1EAF9}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8632,220 +9055,220 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -8853,7 +9276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3C724C-FAEE-446A-80CE-971D62C51A1B}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8866,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
@@ -8877,67 +9300,67 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -8946,13 +9369,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -8961,13 +9384,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -8976,28 +9399,28 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -9006,13 +9429,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -9021,7 +9444,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -9030,7 +9453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1925C935-4969-4657-904B-A05BF1F62E31}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9046,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
@@ -9057,7 +9480,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -9066,13 +9489,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -9081,13 +9504,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -9096,13 +9519,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -9111,13 +9534,13 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -9126,13 +9549,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -9141,15 +9564,15 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -9158,15 +9581,15 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -9175,15 +9598,15 @@
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -9192,15 +9615,15 @@
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -9209,15 +9632,15 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -9226,11 +9649,263 @@
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E12" s="2" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC21091E-61A0-4AC8-BD10-A8085CB0622E}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>480</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9238,251 +9913,134 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC21091E-61A0-4AC8-BD10-A8085CB0622E}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E6CDBF-F1A2-46E8-A7E3-9651DDF8568E}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.90625" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>328</v>
+        <v>528</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>488</v>
+        <v>534</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>493</v>
+        <v>539</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>484</v>
+        <v>540</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>495</v>
+        <v>542</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>496</v>
+        <v>543</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>499</v>
+        <v>545</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>202</v>
+        <v>546</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>202</v>
+        <v>549</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>202</v>
+        <v>552</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>505</v>
+        <v>554</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>202</v>
+        <v>555</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>507</v>
+        <v>557</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>508</v>
+        <v>558</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>559</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9490,140 +10048,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E6CDBF-F1A2-46E8-A7E3-9651DDF8568E}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="20.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9270D2-1DFD-4609-8DD8-4314AD28BAD5}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9633,195 +10057,195 @@
         <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -9829,229 +10253,229 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F37058-B1AB-44D4-9364-EFF282C7BF6D}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="9" t="s">
         <v>616</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="9" t="s">
         <v>622</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>628</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="9" t="s">
         <v>633</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="9" t="s">
         <v>639</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="9" t="s">
         <v>645</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="F8" s="9" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="9" t="s">
         <v>655</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="F10" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="9" t="s">
         <v>666</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -10071,6 +10495,225 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CFDFB27-E3F7-4E10-92F2-1ED4C2B7E6CC}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F6BECC-F706-4A64-85AF-8FE07BE8DFF1}">
   <dimension ref="A1:E12"/>
@@ -10274,225 +10917,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CFDFB27-E3F7-4E10-92F2-1ED4C2B7E6CC}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CCF85B-1D8B-40D0-8651-858D30832D65}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -10505,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
@@ -10516,7 +10940,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -10525,13 +10949,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -10540,13 +10964,13 @@
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -10555,13 +10979,13 @@
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -10570,13 +10994,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -10585,13 +11009,13 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -10600,13 +11024,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -10615,13 +11039,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -10630,13 +11054,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -10645,13 +11069,13 @@
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -10660,13 +11084,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
@@ -10675,13 +11099,13 @@
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
@@ -10690,13 +11114,13 @@
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
@@ -10705,13 +11129,13 @@
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -10720,13 +11144,13 @@
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
@@ -10735,7 +11159,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -10744,7 +11168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1562B9C4-5EB2-4711-BAA3-5E0E5A457F40}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -10757,10 +11181,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>726</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>727</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>106</v>
@@ -10768,7 +11192,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>12</v>
@@ -10777,13 +11201,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>12</v>
@@ -10792,13 +11216,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>12</v>
@@ -10807,13 +11231,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>12</v>
@@ -10822,15 +11246,15 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>12</v>
@@ -10839,13 +11263,13 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>12</v>
@@ -10854,13 +11278,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>12</v>
@@ -10869,13 +11293,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>12</v>
@@ -10884,13 +11308,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>12</v>
@@ -10899,9 +11323,141 @@
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B60E7A-DB31-4204-A38D-A435066C3089}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10909,138 +11465,6 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B60E7A-DB31-4204-A38D-A435066C3089}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBBE1DF-9B21-458C-9DAB-C531AC9C79D0}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11050,10 +11474,10 @@
         <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
@@ -11064,16 +11488,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="E2" s="2">
         <v>32</v>
@@ -11081,16 +11505,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E3" s="2">
         <v>32</v>
@@ -11098,16 +11522,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E4" s="2">
         <v>32</v>
@@ -11115,16 +11539,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E5" s="2">
         <v>44</v>
@@ -11132,16 +11556,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E6" s="2">
         <v>44</v>
@@ -11149,16 +11573,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E7" s="2">
         <v>66</v>
@@ -11166,16 +11590,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E8" s="2">
         <v>66</v>
@@ -11183,16 +11607,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E9" s="2">
         <v>48</v>
@@ -11200,16 +11624,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E10" s="2">
         <v>71</v>
@@ -11217,16 +11641,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E11" s="2">
         <v>46</v>
@@ -11237,7 +11661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2B2B59-9115-4585-B375-F1C67961EBE1}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11251,10 +11675,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -11265,61 +11689,61 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -11328,7 +11752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054EF060-A630-48C2-A9DF-7F5D0119D437}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11340,10 +11764,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>58</v>
@@ -11352,128 +11776,344 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>823</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>825</v>
       </c>
+      <c r="E9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B24131-3A5B-4A23-AA50-C24BEEDC60FF}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11481,196 +12121,25 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B24131-3A5B-4A23-AA50-C24BEEDC60FF}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ACE019-B313-42D9-92EE-5813F3E542B0}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.81640625" customWidth="1"/>
+    <col min="1" max="1" width="39.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>848</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>106</v>
@@ -11678,24 +12147,24 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>851</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -11704,15 +12173,15 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -11721,15 +12190,15 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -11738,15 +12207,15 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>858</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -11755,15 +12224,15 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>861</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -11772,15 +12241,15 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>864</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -11789,15 +12258,15 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>867</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -11806,15 +12275,15 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>870</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -11823,15 +12292,15 @@
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -11840,15 +12309,15 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -11857,15 +12326,15 @@
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>877</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -11874,15 +12343,15 @@
         <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
@@ -11891,15 +12360,15 @@
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>882</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
@@ -11908,10 +12377,10 @@
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>885</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -11935,7 +12404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B682A30B-8658-44C2-B03C-BE99032575E1}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11945,10 +12414,10 @@
         <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>86</v>
@@ -11959,142 +12428,142 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>890</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>891</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>899</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>900</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>903</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>904</v>
       </c>
       <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>902</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>906</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>907</v>
       </c>
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>909</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>910</v>
       </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>12</v>
@@ -12103,13 +12572,13 @@
         <v>132</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>12</v>
@@ -12118,13 +12587,13 @@
         <v>132</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>12</v>
@@ -12133,26 +12602,233 @@
         <v>17</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>920</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>921</v>
-      </c>
       <c r="E14" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B2E160-BFAA-4854-BC33-9A47D7F27CDB}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1059</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12342,15 +13018,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B2E160-BFAA-4854-BC33-9A47D7F27CDB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DB6997-6582-44D0-B6D2-26EB82DB191F}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12369,12 +13036,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>6</v>
@@ -12383,13 +13050,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>12</v>
@@ -12398,13 +13065,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>12</v>
@@ -12413,13 +13080,13 @@
         <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>6</v>
@@ -12428,13 +13095,13 @@
         <v>7</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>12</v>
@@ -12443,13 +13110,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>12</v>
@@ -12458,13 +13125,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>12</v>
@@ -12473,13 +13140,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>12</v>
@@ -12488,13 +13155,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>12</v>
@@ -12503,13 +13170,13 @@
         <v>7</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>12</v>
@@ -12518,24 +13185,349 @@
         <v>17</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>945</v>
-      </c>
       <c r="E12" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FE890E-88CF-4AF3-8148-616067257EFF}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="61.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>919</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12543,198 +13535,6 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FE890E-88CF-4AF3-8148-616067257EFF}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>923</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>924</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>925</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>926</v>
-      </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>927</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>928</v>
-      </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>927</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>929</v>
-      </c>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>930</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>932</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>936</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>937</v>
-      </c>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>939</v>
-      </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>940</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>941</v>
-      </c>
-      <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>943</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>945</v>
-      </c>
-      <c r="E12" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B2B9AA-3C0E-40B2-83F8-F6623874DA4E}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12753,12 +13553,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
@@ -12767,12 +13567,12 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -12781,12 +13581,12 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -12795,12 +13595,12 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -12809,12 +13609,12 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -12823,12 +13623,12 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -12837,12 +13637,12 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -12851,12 +13651,12 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -12865,40 +13665,40 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>965</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -12907,12 +13707,12 @@
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -12921,12 +13721,12 @@
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -12935,7 +13735,7 @@
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -13296,7 +14096,8 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13759,146 +14560,224 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86346C5-FDC7-417E-BC03-2E8E8C009A75}">
-  <dimension ref="B1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB9D776-DCAA-4FAA-912F-014A0B8F4ACE}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.1796875" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" customWidth="1"/>
+    <col min="1" max="1" width="84.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>976</v>
-      </c>
-      <c r="C1" t="s">
-        <v>977</v>
-      </c>
-      <c r="D1" t="s">
-        <v>978</v>
-      </c>
-      <c r="E1" t="s">
-        <v>979</v>
-      </c>
-      <c r="F1" t="s">
-        <v>980</v>
-      </c>
-      <c r="G1" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>982</v>
-      </c>
-      <c r="C2" t="s">
-        <v>983</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>982</v>
-      </c>
-      <c r="C3" t="s">
-        <v>983</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>982</v>
-      </c>
-      <c r="C4" t="s">
-        <v>983</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>982</v>
-      </c>
-      <c r="C5" t="s">
-        <v>983</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>982</v>
-      </c>
-      <c r="C6" t="s">
-        <v>986</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>982</v>
-      </c>
-      <c r="C7" t="s">
-        <v>986</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>982</v>
-      </c>
-      <c r="C8" t="s">
-        <v>986</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>982</v>
-      </c>
-      <c r="C9" t="s">
-        <v>986</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>985</v>
-      </c>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13906,8 +14785,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB9D776-DCAA-4FAA-912F-014A0B8F4ACE}">
-  <dimension ref="A1:E14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74906B5F-BBD2-4E50-AA59-4D76843BE3DD}">
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -13918,209 +14797,201 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>295</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84173879-A876-4F8F-8D71-F80C6BBA6E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC6D7BB-436D-4A6B-8C24-F135E0020084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="28" activeTab="31" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="9" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Paclitaxel" sheetId="1" r:id="rId1"/>
@@ -8643,6 +8643,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A417E582-1074-4E3F-A381-7D1E4C5C9732}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.26953125" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -9049,6 +9053,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5758C6-ECFE-417C-B9EA-14BCA8C1EAF9}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="66.08984375" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" customWidth="1"/>
+    <col min="3" max="3" width="80.54296875" customWidth="1"/>
+    <col min="4" max="4" width="50.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -9280,6 +9290,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3C724C-FAEE-446A-80CE-971D62C51A1B}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="80.08984375" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -9917,7 +9931,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.90625" customWidth="1"/>
+    <col min="1" max="1" width="70.6328125" customWidth="1"/>
     <col min="2" max="2" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10051,6 +10065,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9270D2-1DFD-4609-8DD8-4314AD28BAD5}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34.36328125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -10499,6 +10518,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CFDFB27-E3F7-4E10-92F2-1ED4C2B7E6CC}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" customWidth="1"/>
+    <col min="3" max="3" width="26.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -11172,6 +11196,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1562B9C4-5EB2-4711-BAA3-5E0E5A457F40}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -11336,6 +11363,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B60E7A-DB31-4204-A38D-A435066C3089}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -11666,7 +11696,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
     <col min="2" max="2" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11757,7 +11787,7 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="51.26953125" customWidth="1"/>
     <col min="3" max="3" width="20.453125" customWidth="1"/>
     <col min="4" max="4" width="24.54296875" customWidth="1"/>
   </cols>
@@ -11908,6 +11938,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B24131-3A5B-4A23-AA50-C24BEEDC60FF}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -12408,6 +12441,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B682A30B-8658-44C2-B03C-BE99032575E1}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="75.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
@@ -12633,7 +12669,7 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="61.26953125" customWidth="1"/>
     <col min="2" max="2" width="19.26953125" customWidth="1"/>
     <col min="3" max="3" width="12.7265625" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" customWidth="1"/>

--- a/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
+++ b/singscore_new_code/results/Deep_search_results/deepsearch_1_RAW_data_prompt1_results_tab_extraction_drug_pathway_direction_indication_reasoning_citation.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GS\PySingscore_replicate\singscore_new_code\results\Deep_search_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC6D7BB-436D-4A6B-8C24-F135E0020084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0914203-6521-4EC9-8762-315C4F40A2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="9" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FEF4C8FA-A983-4EE7-8B89-84DD9ADD6E7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Paclitaxel" sheetId="1" r:id="rId1"/>
@@ -8644,8 +8644,9 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.26953125" customWidth="1"/>
-    <col min="3" max="3" width="53.7265625" customWidth="1"/>
+    <col min="1" max="1" width="70.6328125" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+    <col min="3" max="3" width="27.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
